--- a/stories/arbres/ATOM-EMO.LEX.006-02.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.006-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Dehors, un camion passe. Le bruit est fort. Les vitres vibrent un peu. Rayan est dans le salon. Il entend le vrombissement. Son ventre se serre. Ses mains deviennent chaudes. Parce que le bruit est fort, Rayan se sent petit. Rayan dit : je suis inquiet. Il va vers maman. Maman est l'adulte près du canapé. Rayan dit : j'ai le ventre serré. Maman dit : tu peux raconter. Rayan raconte le bruit du camion. Maman écoute. Papa arrive aussi. Ils restent tous les trois. Rayan souffle. Son ventre se desserre un peu. Parce qu'il a raconté, il se sent moins seul. Être inquiet, on peut le dire. On va vers un adulte. On peut raconter. Maman lui tient la main. Le salon redevient calme.</t>
+          <t>Dehors, un camion passe. Le bruit est fort. Les vitres vibrent un peu. Rayan est dans le salon. Il entend le vrombissement. Son ventre se serre. Ses mains deviennent chaudes. Parce que le bruit est fort, Rayan se sent petit. Je suis inquiet. Il va vers maman. Maman est l'adulte près du canapé. J'ai le ventre serré. Tu peux raconter. Rayan raconte le bruit du camion. Maman écoute. Papa arrive aussi. Ils restent tous les trois. Rayan souffle. Son ventre se desserre un peu. Parce qu'il a raconté, il se sent moins seul. Être inquiet, on peut le dire. On va vers un adulte. On peut raconter. Maman lui tient la main. Le salon redevient calme.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Dehors, un camion passe. Le bruit est fort. Les vitres vibrent un peu. Rayan est dans le salon. Il entend le vrombissement. Son ventre se serre. Ses mains deviennent chaudes. Parce que le bruit est fort, Rayan se sent petit.
+enfant-m|Je suis inquiet. Il va vers maman. Maman est l'adulte près du canapé.
+enfant-m|J'ai le ventre serré.
+maman|Tu peux raconter.
+narrateur|Rayan raconte le bruit du camion. Maman écoute. Papa arrive aussi. Ils restent tous les trois. Rayan souffle. Son ventre se desserre un peu. Parce qu'il a raconté, il se sent moins seul. Être inquiet, on peut le dire. On va vers un adulte. On peut raconter. Maman lui tient la main. Le salon redevient calme.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Rayan a le ventre serré. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Rayan a nommé : inquiet. Il a rejoint un adulte. Il a pu raconter.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1826,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Le camion s'éloigne. Rayan reste près de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1993,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2033,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.006-02.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.006-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,11 @@
 narrateur|Rayan raconte le bruit du camion. Maman écoute. Papa arrive aussi. Ils restent tous les trois. Rayan souffle. Son ventre se desserre un peu. Parce qu'il a raconté, il se sent moins seul. Être inquiet, on peut le dire. On va vers un adulte. On peut raconter. Maman lui tient la main. Le salon redevient calme.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1507,7 @@
           <t>narrateur|Rayan a le ventre serré. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1679,7 @@
           <t>narrateur|Rayan a nommé : inquiet. Il a rejoint un adulte. Il a pu raconter.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1831,6 +1843,7 @@
           <t>narrateur|Le camion s'éloigne. Rayan reste près de maman.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1998,6 +2011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2016,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2040,6 +2054,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2241,6 +2269,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-EMO.LEX.006-02.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.006-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rayan est inquiet dans le salon</t>
+          <t>Le camion d'Amir</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,7 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +831,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un camion passe. Le verre tremble. Amir a le ventre serré. Il dit qu'il est inquiet. Il raconte à maman. Papa vient.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1185,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Dehors, un camion passe. Le bruit est fort. Les vitres vibrent un peu. Rayan est dans le salon. Il entend le vrombissement. Son ventre se serre. Ses mains deviennent chaudes. Parce que le bruit est fort, Rayan se sent petit. Je suis inquiet. Il va vers maman. Maman est l'adulte près du canapé. J'ai le ventre serré. Tu peux raconter. Rayan raconte le bruit du camion. Maman écoute. Papa arrive aussi. Ils restent tous les trois. Rayan souffle. Son ventre se desserre un peu. Parce qu'il a raconté, il se sent moins seul. Être inquiet, on peut le dire. On va vers un adulte. On peut raconter. Maman lui tient la main. Le salon redevient calme.</t>
+          <t>Le verre d'eau tremble tout seul. Un rond bouge à la surface. L'abat-jour de la lampe frémit. Le plancher vibre un tout petit peu. Un coussin rouge a glissé du canapé. Il est encore chaud du soleil. Une poussière tourne dans le rayon. Le tapis sent un peu la laine. Amir, tu as entendu ça ? Un gros bruit, maman. C'est loin, encore. En ce moment, Amir est dans le salon. Dehors, un camion passe. Le bruit est fort. Les vitres vibrent un peu. Amir entend le vrombissement. Son ventre se serre. Ses mains deviennent chaudes. Parce que le bruit est fort, Amir se sent petit. Je suis inquiet. Il va vers maman. Maman est l'adulte près du canapé. J'ai le ventre serré. Tu peux raconter. Le camion fait un gros bruit. Je t'écoute, Amir. Être inquiet, ce n'est pas honteux. Amir raconte le bruit du camion. Le coussin rouge est au sol. J'arrive aussi. On reste tous les trois. Le ventre est encore un peu serré. Tu as dit : je suis inquiet. Bravo, Amir. Tu es venu vers un adulte. Tu as pu raconter. Tu as fait du bon travail. Amir souffle. Son ventre se desserre un peu. Parce qu'il a raconté, il se sent moins seul. Tu veux ma main ? Oui, papa. Maman lui tient l'autre main. Être inquiet, on peut le dire. On va vers un adulte. On peut raconter. Le verre d'eau ne tremble plus. Tu as tes pieds sur le tapis ? Oui. Le tapis est doux. Le gros bruit s'en va. Le salon redevient calme.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1325,62 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Dehors, un camion passe. Le bruit est fort. Les vitres vibrent un peu. Rayan est dans le salon. Il entend le vrombissement. Son ventre se serre. Ses mains deviennent chaudes. Parce que le bruit est fort, Rayan se sent petit.
-enfant-m|Je suis inquiet. Il va vers maman. Maman est l'adulte près du canapé.
+          <t>narrateur|Le verre d'eau tremble tout seul.
+narrateur|Un rond bouge à la surface.
+narrateur|L'abat-jour de la lampe frémit.
+narrateur|Le plancher vibre un tout petit peu.
+narrateur|Un coussin rouge a glissé du canapé.
+narrateur|Il est encore chaud du soleil.
+narrateur|Une poussière tourne dans le rayon.
+narrateur|Le tapis sent un peu la laine.
+maman|Amir, tu as entendu ça ?
+enfant-m|Un gros bruit, maman.
+papa|C'est loin, encore.
+narrateur|En ce moment, Amir est dans le salon.
+narrateur|Dehors, un camion passe.
+narrateur|Le bruit est fort.
+narrateur|Les vitres vibrent un peu.
+narrateur|Amir entend le vrombissement.
+narrateur|Son ventre se serre.
+narrateur|Ses mains deviennent chaudes.
+narrateur|Parce que le bruit est fort, Amir se sent petit.
+enfant-m|Je suis inquiet.
+narrateur|Il va vers maman.
+narrateur|Maman est l'adulte près du canapé.
 enfant-m|J'ai le ventre serré.
 maman|Tu peux raconter.
-narrateur|Rayan raconte le bruit du camion. Maman écoute. Papa arrive aussi. Ils restent tous les trois. Rayan souffle. Son ventre se desserre un peu. Parce qu'il a raconté, il se sent moins seul. Être inquiet, on peut le dire. On va vers un adulte. On peut raconter. Maman lui tient la main. Le salon redevient calme.</t>
+enfant-m|Le camion fait un gros bruit.
+maman|Je t'écoute, Amir.
+maman|Être inquiet, ce n'est pas honteux.
+narrateur|Amir raconte le bruit du camion.
+narrateur|Le coussin rouge est au sol.
+papa|J'arrive aussi.
+papa|On reste tous les trois.
+enfant-m|Le ventre est encore un peu serré.
+papa|Tu as dit : je suis inquiet.
+papa|Bravo, Amir.
+maman|Tu es venu vers un adulte.
+maman|Tu as pu raconter.
+maman|Tu as fait du bon travail.
+narrateur|Amir souffle.
+narrateur|Son ventre se desserre un peu.
+narrateur|Parce qu'il a raconté, il se sent moins seul.
+papa|Tu veux ma main ?
+enfant-m|Oui, papa.
+narrateur|Maman lui tient l'autre main.
+narrateur|Être inquiet, on peut le dire.
+narrateur|On va vers un adulte.
+narrateur|On peut raconter.
+narrateur|Le verre d'eau ne tremble plus.
+maman|Tu as tes pieds sur le tapis ?
+enfant-m|Oui. Le tapis est doux.
+papa|Le gros bruit s'en va.
+narrateur|Le salon redevient calme.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>enfants_parc</t>
+          <t>voiture_passe</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1407,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Rayan a le ventre serré. Que fait-il ?</t>
+          <t>Amir a le ventre serré. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,7 +1563,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Rayan a le ventre serré. Que fait-il ?</t>
+          <t>narrateur|Amir a le ventre serré.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1532,7 +1592,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Rayan a nommé : inquiet. Il a rejoint un adulte. Il a pu raconter.</t>
+          <t>Amir a nommé : inquiet. Il a rejoint un adulte. Il a pu raconter. Je suis inquiet. Oui. Tu as raconté le camion. Bravo, Amir. Tu as fait du bon travail. Mon ventre est moins serré. Tu peux encore raconter, si tu veux. Le coussin rouge est sur le canapé. L'abat-jour ne frémit plus.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1676,7 +1736,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Rayan a nommé : inquiet. Il a rejoint un adulte. Il a pu raconter.</t>
+          <t>narrateur|Amir a nommé : inquiet.
+narrateur|Il a rejoint un adulte.
+narrateur|Il a pu raconter.
+enfant-m|Je suis inquiet.
+maman|Oui.
+maman|Tu as raconté le camion.
+papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+enfant-m|Mon ventre est moins serré.
+maman|Tu peux encore raconter, si tu veux.
+narrateur|Le coussin rouge est sur le canapé.
+narrateur|L'abat-jour ne frémit plus.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1704,7 +1775,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Le camion s'éloigne. Rayan reste près de maman.</t>
+          <t>Le camion s'éloigne. Amir reste près de maman. Tu veux une gorgée d'eau ? Oui. Le verre ne tremble plus. L'eau est fraîche. C'est calme, maintenant. Tu as dit ton inquiétude. C'est du bon travail. On reste encore un peu ici ? Oui, papa. Le plancher ne vibre plus. Le salon est tout calme.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1840,7 +1911,19 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Le camion s'éloigne. Rayan reste près de maman.</t>
+          <t>narrateur|Le camion s'éloigne.
+narrateur|Amir reste près de maman.
+maman|Tu veux une gorgée d'eau ?
+enfant-m|Oui.
+narrateur|Le verre ne tremble plus.
+papa|L'eau est fraîche.
+enfant-m|C'est calme, maintenant.
+maman|Tu as dit ton inquiétude.
+maman|C'est du bon travail.
+papa|On reste encore un peu ici ?
+enfant-m|Oui, papa.
+narrateur|Le plancher ne vibre plus.
+narrateur|Le salon est tout calme.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1868,7 +1951,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai dit : je suis inquiet. J'ai raconté à maman. Être inquiet, on peut le dire. Bravo, Amir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2008,7 +2091,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai dit : je suis inquiet.
+enfant-m|J'ai raconté à maman.
+maman|Être inquiet, on peut le dire.
+papa|Bravo, Amir.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2030,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2068,6 +2155,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.006-02.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.006-02.xlsx
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le verre d'eau tremble tout seul. Un rond bouge à la surface. L'abat-jour de la lampe frémit. Le plancher vibre un tout petit peu. Un coussin rouge a glissé du canapé. Il est encore chaud du soleil. Une poussière tourne dans le rayon. Le tapis sent un peu la laine. Amir, tu as entendu ça ? Un gros bruit, maman. C'est loin, encore. En ce moment, Amir est dans le salon. Dehors, un camion passe. Le bruit est fort. Les vitres vibrent un peu. Amir entend le vrombissement. Son ventre se serre. Ses mains deviennent chaudes. Parce que le bruit est fort, Amir se sent petit. Je suis inquiet. Il va vers maman. Maman est l'adulte près du canapé. J'ai le ventre serré. Tu peux raconter. Le camion fait un gros bruit. Je t'écoute, Amir. Être inquiet, ce n'est pas honteux. Amir raconte le bruit du camion. Le coussin rouge est au sol. J'arrive aussi. On reste tous les trois. Le ventre est encore un peu serré. Tu as dit : je suis inquiet. Bravo, Amir. Tu es venu vers un adulte. Tu as pu raconter. Tu as fait du bon travail. Amir souffle. Son ventre se desserre un peu. Parce qu'il a raconté, il se sent moins seul. Tu veux ma main ? Oui, papa. Maman lui tient l'autre main. Être inquiet, on peut le dire. On va vers un adulte. On peut raconter. Le verre d'eau ne tremble plus. Tu as tes pieds sur le tapis ? Oui. Le tapis est doux. Le gros bruit s'en va. Le salon redevient calme.</t>
+          <t>Le verre d'eau tremble tout seul. Un rond bouge à la surface. L'abat-jour de la lampe frémit. Le plancher vibre un tout petit peu. Un coussin rouge a glissé du canapé. Il est encore chaud du soleil. Une poussière tourne dans le rayon. Le tapis sent un peu la laine. Amir, tu as entendu ça ? Un gros bruit, maman. C'est loin, encore. En ce moment, Amir est dans le salon. Dehors, un camion passe. Le bruit est fort. Les vitres vibrent un peu. Amir entend le vrombissement. Son ventre se serre. Ses mains deviennent chaudes. Parce que le bruit est fort, Amir se sent petit. Je suis inquiet. Il va vers maman. Maman est l'adulte près du canapé. J'ai le ventre serré. Tu peux raconter. Le camion fait un gros bruit. Je t'écoute, Amir. Être inquiet, ce n'est pas honteux. Amir raconte le bruit du camion. Le coussin rouge est au sol. J'arrive aussi. On reste tous les trois. Le ventre est encore un peu serré. Tu as dit : je suis inquiet. Bravo, Amir. Tu es venu vers un adulte. Tu as pu raconter. Amir souffle. Son ventre se desserre un peu. Parce qu'il a raconté, il se sent moins seul. Tu veux ma main ? Oui, papa. Maman lui tient l'autre main. Être inquiet, on peut le dire. On va vers un adulte. On peut raconter. Le verre d'eau ne tremble plus. Tu as tes pieds sur le tapis ? Oui. Le tapis est doux. Le gros bruit s'en va. Le salon redevient calme.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Dehors, un camion passe. Le bruit est fort. Les vitres vibrent un peu. Rayan est dans le salon. Il entend le vrombissement. Son ventre se serre. Ses mains deviennent chaudes. Parce que le bruit est fort, Rayan se sent petit. Rayan dit : je suis &lt;emphasis level="moderate"&gt;inquiet&lt;/emphasis&gt;. Il va vers maman. Maman est l'adulte près du canapé. Rayan dit : j'ai le ventre serré. Maman dit : tu peux raconter. Rayan raconte le bruit du camion. Maman écoute. Papa arrive aussi. Ils restent tous les trois. Rayan souffle. Son ventre se desserre un peu. Parce qu'il a raconté, il se sent moins seul. Être inquiet, on peut le dire. On va vers un adulte. On peut raconter. Maman lui tient la main. Le salon redevient calme.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le verre d'eau tremble tout seul. Un rond bouge à la surface. L'abat-jour de la lampe frémit. Le plancher vibre un tout petit peu. Un coussin rouge a glissé du canapé. Il est encore chaud du soleil. Une poussière tourne dans le rayon. Le tapis sent un peu la laine. Amir, tu as entendu ça ? Un gros bruit, maman. C'est loin, encore. En ce moment, Amir est dans le salon. Dehors, un camion passe. Le bruit est fort. Les vitres vibrent un peu. Amir entend le vrombissement. Son ventre se serre. Ses mains deviennent chaudes. Parce que le bruit est fort, Amir se sent petit. Je suis inquiet. Il va vers maman. Maman est l'adulte près du canapé. J'ai le ventre serré. Tu peux raconter. Le camion fait un gros bruit. Je t'écoute, Amir. Être inquiet, ce n'est pas honteux. Amir raconte le bruit du camion. Le coussin rouge est au sol. J'arrive aussi. On reste tous les trois. Le ventre est encore un peu serré. Tu as dit : je suis inquiet. Bravo, Amir. Tu es venu vers un adulte. Tu as pu raconter. Amir souffle. Son ventre se desserre un peu. Parce qu'il a raconté, il se sent moins seul. Tu veux ma main ? Oui, papa. Maman lui tient l'autre main. Être inquiet, on peut le dire. On va vers un adulte. On peut raconter. Le verre d'eau ne tremble plus. Tu as tes pieds sur le tapis ? Oui. Le tapis est doux. Le gros bruit s'en va. Le salon redevient calme.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1361,7 +1361,6 @@
 papa|Bravo, Amir.
 maman|Tu es venu vers un adulte.
 maman|Tu as pu raconter.
-maman|Tu as fait du bon travail.
 narrateur|Amir souffle.
 narrateur|Son ventre se desserre un peu.
 narrateur|Parce qu'il a raconté, il se sent moins seul.
@@ -1412,7 +1411,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Rayan a le ventre serré. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir a le ventre serré. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1567,7 +1566,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1592,12 +1590,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Amir a nommé : inquiet. Il a rejoint un adulte. Il a pu raconter. Je suis inquiet. Oui. Tu as raconté le camion. Bravo, Amir. Tu as fait du bon travail. Mon ventre est moins serré. Tu peux encore raconter, si tu veux. Le coussin rouge est sur le canapé. L'abat-jour ne frémit plus.</t>
+          <t>Amir a nommé : inquiet. Il a rejoint un adulte. Il a pu raconter. Je suis inquiet. Oui. Tu as raconté le camion. Bravo, Amir. Mon ventre est moins serré. Tu peux encore raconter, si tu veux. Le coussin rouge est sur le canapé. L'abat-jour ne frémit plus.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Rayan a nommé : &lt;emphasis level="moderate"&gt;inquiet&lt;/emphasis&gt;. Il a rejoint un adulte. Il a pu raconter.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir a nommé : inquiet. Il a rejoint un adulte. Il a pu raconter. Je suis inquiet. Oui. Tu as raconté le camion. Bravo, Amir. Mon ventre est moins serré. Tu peux encore raconter, si tu veux. Le coussin rouge est sur le canapé. L'abat-jour ne frémit plus.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1743,14 +1741,12 @@
 maman|Oui.
 maman|Tu as raconté le camion.
 papa|Bravo, Amir.
-papa|Tu as fait du bon travail.
 enfant-m|Mon ventre est moins serré.
 maman|Tu peux encore raconter, si tu veux.
 narrateur|Le coussin rouge est sur le canapé.
 narrateur|L'abat-jour ne frémit plus.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1775,12 +1771,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Le camion s'éloigne. Amir reste près de maman. Tu veux une gorgée d'eau ? Oui. Le verre ne tremble plus. L'eau est fraîche. C'est calme, maintenant. Tu as dit ton inquiétude. C'est du bon travail. On reste encore un peu ici ? Oui, papa. Le plancher ne vibre plus. Le salon est tout calme.</t>
+          <t>Le camion s'éloigne. Amir reste près de maman. Tu veux une gorgée d'eau ? Oui. Le verre ne tremble plus. L'eau est fraîche. C'est calme, maintenant. Tu as dit ton inquiétude. On reste encore un peu ici ? Oui, papa. Le plancher ne vibre plus. Le salon est tout calme.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le camion s'éloigne. Rayan reste près de maman.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le camion s'éloigne. Amir reste près de maman. Tu veux une gorgée d'eau ? Oui. Le verre ne tremble plus. L'eau est fraîche. C'est calme, maintenant. Tu as dit ton inquiétude. On reste encore un peu ici ? Oui, papa. Le plancher ne vibre plus. Le salon est tout calme.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1919,14 +1915,12 @@
 papa|L'eau est fraîche.
 enfant-m|C'est calme, maintenant.
 maman|Tu as dit ton inquiétude.
-maman|C'est du bon travail.
 papa|On reste encore un peu ici ?
 enfant-m|Oui, papa.
 narrateur|Le plancher ne vibre plus.
 narrateur|Le salon est tout calme.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1951,12 +1945,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit : je suis inquiet. J'ai raconté à maman. Être inquiet, on peut le dire. Bravo, Amir. L'histoire est finie.</t>
+          <t>J'ai dit : je suis inquiet. J'ai raconté à maman. Être inquiet, on peut le dire. Bravo, Amir.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai dit : je suis inquiet. J'ai raconté à maman. Être inquiet, on peut le dire. Bravo, Amir.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2094,11 +2088,9 @@
           <t>enfant-m|J'ai dit : je suis inquiet.
 enfant-m|J'ai raconté à maman.
 maman|Être inquiet, on peut le dire.
-papa|Bravo, Amir.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+papa|Bravo, Amir.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2117,7 +2109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2162,6 +2154,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.006-02.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.006-02.xlsx
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -672,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>maison</t>
+          <t>salon, après-midi</t>
         </is>
       </c>
     </row>
@@ -684,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rayan, maman, papa</t>
+          <t>Amir, maman, papa</t>
         </is>
       </c>
     </row>
